--- a/data/trans_orig/P05A04-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P05A04-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su barrio se encuentra afectado por alguna industria contaminante en 2007</t>
+          <t>Población según si su barrio se encuentra afectado por alguna industria contaminante en 2007 (tasa de respuesta: 99,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>403502</t>
+          <t>404572</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>430976</t>
+          <t>431049</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>255893</t>
+          <t>255953</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>279688</t>
+          <t>278694</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>667544</t>
+          <t>668565</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>703990</t>
+          <t>703147</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,91%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24969</t>
+          <t>24489</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48805</t>
+          <t>47571</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21068</t>
+          <t>21186</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42091</t>
+          <t>42543</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>50508</t>
+          <t>51898</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>84651</t>
+          <t>82164</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,62%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7554</t>
+          <t>7601</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22496</t>
+          <t>23367</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2203</t>
+          <t>2287</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13289</t>
+          <t>13517</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12864</t>
+          <t>12412</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>31274</t>
+          <t>30058</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>306780</t>
+          <t>305335</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>331195</t>
+          <t>332104</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>323859</t>
+          <t>323741</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>345873</t>
+          <t>346127</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>638401</t>
+          <t>636364</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>674644</t>
+          <t>672499</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,65%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26628</t>
+          <t>25799</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>50043</t>
+          <t>51406</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15389</t>
+          <t>15342</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34557</t>
+          <t>34710</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>47032</t>
+          <t>46542</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>77821</t>
+          <t>77873</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3609</t>
+          <t>2868</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15123</t>
+          <t>15858</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3840</t>
+          <t>4040</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17046</t>
+          <t>16504</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9379</t>
+          <t>9505</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27481</t>
+          <t>27265</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>459174</t>
+          <t>458159</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>489635</t>
+          <t>488580</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>146122</t>
+          <t>144154</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>160547</t>
+          <t>159929</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>611628</t>
+          <t>612461</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>644173</t>
+          <t>645242</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,57%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39173</t>
+          <t>40120</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67208</t>
+          <t>67840</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7064</t>
+          <t>7142</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20827</t>
+          <t>22116</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51636</t>
+          <t>49866</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>81557</t>
+          <t>81223</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>3901</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18183</t>
+          <t>18636</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5214</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4494</t>
+          <t>4662</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19406</t>
+          <t>20830</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1073803</t>
+          <t>1074193</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1116916</t>
+          <t>1117758</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>620023</t>
+          <t>621867</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>652359</t>
+          <t>652828</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1706629</t>
+          <t>1707144</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1760394</t>
+          <t>1760332</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>93789</t>
+          <t>93078</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>134872</t>
+          <t>134151</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39646</t>
+          <t>39982</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>68694</t>
+          <t>68752</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>140073</t>
+          <t>141844</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>191270</t>
+          <t>191523</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10882</t>
+          <t>10257</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27039</t>
+          <t>27091</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9699</t>
+          <t>9696</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>24809</t>
+          <t>24521</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>23427</t>
+          <t>22956</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>45200</t>
+          <t>44497</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>294468</t>
+          <t>295543</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>317692</t>
+          <t>318362</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>471506</t>
+          <t>471737</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>504835</t>
+          <t>505400</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>776188</t>
+          <t>776030</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>815880</t>
+          <t>815497</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,58%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20860</t>
+          <t>20353</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>41098</t>
+          <t>40295</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>46986</t>
+          <t>47392</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>78284</t>
+          <t>78841</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>74965</t>
+          <t>73804</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>112402</t>
+          <t>110290</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17041</t>
+          <t>16617</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7018</t>
+          <t>7048</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23443</t>
+          <t>21717</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13869</t>
+          <t>13947</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>32175</t>
+          <t>32419</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>263055</t>
+          <t>262779</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>281252</t>
+          <t>280923</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1074890</t>
+          <t>1076099</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1118557</t>
+          <t>1119363</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1346520</t>
+          <t>1347274</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1393854</t>
+          <t>1394670</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,28%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13822</t>
+          <t>13931</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>31166</t>
+          <t>31354</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>85743</t>
+          <t>88038</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>125726</t>
+          <t>126504</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>104970</t>
+          <t>104639</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>150444</t>
+          <t>150353</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6291</t>
+          <t>6463</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>18314</t>
+          <t>17778</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>38240</t>
+          <t>38052</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>19589</t>
+          <t>19493</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>42137</t>
+          <t>41785</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2853361</t>
+          <t>2852518</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2923923</t>
+          <t>2923594</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2948297</t>
+          <t>2944731</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3021038</t>
+          <t>3019252</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5829258</t>
+          <t>5829747</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5927122</t>
+          <t>5928184</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,05%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>259358</t>
+          <t>257207</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>323208</t>
+          <t>325849</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>254018</t>
+          <t>255676</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>318185</t>
+          <t>321514</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>525288</t>
+          <t>529950</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>618596</t>
+          <t>622028</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>43275</t>
+          <t>43877</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>75607</t>
+          <t>75135</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>56459</t>
+          <t>57070</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>91573</t>
+          <t>91252</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>108980</t>
+          <t>109644</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>156404</t>
+          <t>154669</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su barrio se encuentra afectado por alguna industria contaminante en 2012</t>
+          <t>Población según si su barrio se encuentra afectado por alguna industria contaminante en 2012 (tasa de respuesta: 99,17%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>387285</t>
+          <t>387512</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>410410</t>
+          <t>410324</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>269978</t>
+          <t>268984</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>290587</t>
+          <t>289753</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>665088</t>
+          <t>663704</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>695721</t>
+          <t>695132</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,44%</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15625</t>
+          <t>14658</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34598</t>
+          <t>34000</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10999</t>
+          <t>11582</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29207</t>
+          <t>29415</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31564</t>
+          <t>30636</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57823</t>
+          <t>57223</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6873</t>
+          <t>7314</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21038</t>
+          <t>21452</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3504</t>
+          <t>3629</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13678</t>
+          <t>14995</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12899</t>
+          <t>12339</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30048</t>
+          <t>30524</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>347205</t>
+          <t>345627</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>376486</t>
+          <t>376270</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>288369</t>
+          <t>289096</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>312542</t>
+          <t>312019</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>645352</t>
+          <t>643622</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>682618</t>
+          <t>681521</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,09%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25552</t>
+          <t>24458</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>50962</t>
+          <t>49758</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18148</t>
+          <t>18814</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39045</t>
+          <t>39423</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>48080</t>
+          <t>48741</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>83182</t>
+          <t>83095</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,11%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6953</t>
+          <t>7941</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25157</t>
+          <t>27232</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1839</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13284</t>
+          <t>13568</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11533</t>
+          <t>11245</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32904</t>
+          <t>32573</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>558898</t>
+          <t>558570</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>586825</t>
+          <t>587672</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>230546</t>
+          <t>232100</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>246839</t>
+          <t>246969</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>795850</t>
+          <t>798240</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>830418</t>
+          <t>831402</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,42%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32579</t>
+          <t>31374</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59081</t>
+          <t>60172</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5949</t>
+          <t>6006</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18857</t>
+          <t>18500</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41726</t>
+          <t>40501</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>73646</t>
+          <t>71372</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2904</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13853</t>
+          <t>14514</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11132</t>
+          <t>10102</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5145</t>
+          <t>5026</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>21205</t>
+          <t>19350</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1036018</t>
+          <t>1038194</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1075145</t>
+          <t>1077497</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>673894</t>
+          <t>673476</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>706602</t>
+          <t>706733</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1719557</t>
+          <t>1720897</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1773218</t>
+          <t>1772283</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,71%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>52514</t>
+          <t>51267</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>85933</t>
+          <t>85861</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41035</t>
+          <t>41439</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>69183</t>
+          <t>70035</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>101522</t>
+          <t>100239</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>145167</t>
+          <t>144619</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16861</t>
+          <t>15983</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>39075</t>
+          <t>37642</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8076</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23826</t>
+          <t>25339</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>29408</t>
+          <t>28364</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>56438</t>
+          <t>54384</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>452592</t>
+          <t>452847</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>476472</t>
+          <t>476812</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>679557</t>
+          <t>680130</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>711067</t>
+          <t>711539</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1142911</t>
+          <t>1143157</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1181520</t>
+          <t>1182243</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,79%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>21906</t>
+          <t>20945</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>42776</t>
+          <t>42394</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>34855</t>
+          <t>34859</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>62010</t>
+          <t>62519</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>61807</t>
+          <t>61251</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>95628</t>
+          <t>97541</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3924</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16269</t>
+          <t>16681</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5059</t>
+          <t>4855</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20077</t>
+          <t>18288</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12196</t>
+          <t>10647</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30411</t>
+          <t>28539</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>226269</t>
+          <t>227253</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>246115</t>
+          <t>246694</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>975880</t>
+          <t>978341</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1015701</t>
+          <t>1016641</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1213853</t>
+          <t>1212627</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1258330</t>
+          <t>1257554</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,13%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16234</t>
+          <t>15536</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>35539</t>
+          <t>33958</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>66189</t>
+          <t>66350</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>102818</t>
+          <t>102038</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>88854</t>
+          <t>87350</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>127589</t>
+          <t>127757</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7319</t>
+          <t>6741</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12293</t>
+          <t>12100</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>30958</t>
+          <t>30140</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>13483</t>
+          <t>13848</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>32235</t>
+          <t>33868</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3063139</t>
+          <t>3061529</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3132553</t>
+          <t>3131212</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3174962</t>
+          <t>3177001</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3245586</t>
+          <t>3246936</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6259039</t>
+          <t>6266091</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6355874</t>
+          <t>6357607</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,01%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>196353</t>
+          <t>197366</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>259862</t>
+          <t>258641</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>212483</t>
+          <t>212709</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>276264</t>
+          <t>274651</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>427254</t>
+          <t>424848</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>510717</t>
+          <t>510072</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>52669</t>
+          <t>53567</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>90155</t>
+          <t>89304</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>46555</t>
+          <t>46214</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>79644</t>
+          <t>78973</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,47 +7171,47 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>130710</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>108701</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>156858</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
           <t>2,27%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>130710</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>110436</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>157913</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="W30" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -7390,7 +7390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su barrio se encuentra afectado por alguna industria contaminante en 2016</t>
+          <t>Población según si su barrio se encuentra afectado por alguna industria contaminante en 2016 (tasa de respuesta: 99,13%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7585,12 +7585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>371904</t>
+          <t>372444</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>397857</t>
+          <t>396884</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>293993</t>
+          <t>293861</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>317281</t>
+          <t>317527</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>674604</t>
+          <t>673700</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>708179</t>
+          <t>710493</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,35%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23069</t>
+          <t>21933</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45768</t>
+          <t>45421</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16704</t>
+          <t>16399</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36463</t>
+          <t>36611</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44003</t>
+          <t>43424</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>74963</t>
+          <t>76053</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3063</t>
+          <t>3041</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14685</t>
+          <t>14136</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5512</t>
+          <t>5891</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19413</t>
+          <t>18782</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11070</t>
+          <t>11609</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>28151</t>
+          <t>28880</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>320858</t>
+          <t>320919</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>346137</t>
+          <t>345295</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>311367</t>
+          <t>311097</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>337236</t>
+          <t>337590</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>643046</t>
+          <t>640428</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>677049</t>
+          <t>678817</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,57%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22358</t>
+          <t>22075</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>45409</t>
+          <t>44321</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23184</t>
+          <t>22453</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46420</t>
+          <t>45696</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>50037</t>
+          <t>47423</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>81818</t>
+          <t>81315</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,97%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3050</t>
+          <t>3108</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14947</t>
+          <t>13834</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4066</t>
+          <t>3375</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16485</t>
+          <t>15625</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9327</t>
+          <t>8909</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25613</t>
+          <t>24769</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>435708</t>
+          <t>436085</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>465673</t>
+          <t>465010</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>140020</t>
+          <t>140530</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>157003</t>
+          <t>157427</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>581450</t>
+          <t>583891</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>617476</t>
+          <t>617272</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,48%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37917</t>
+          <t>37734</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63817</t>
+          <t>63516</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6508</t>
+          <t>6206</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21511</t>
+          <t>21953</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>48734</t>
+          <t>48113</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>80090</t>
+          <t>78314</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,48%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8628</t>
+          <t>8434</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24383</t>
+          <t>23654</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>950</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8263</t>
+          <t>8124</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11270</t>
+          <t>10725</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>28561</t>
+          <t>27668</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>949086</t>
+          <t>950927</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>999918</t>
+          <t>999285</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>711378</t>
+          <t>713309</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>746612</t>
+          <t>746989</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1673782</t>
+          <t>1673255</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1733442</t>
+          <t>1735124</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,67%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>89081</t>
+          <t>90191</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>128031</t>
+          <t>132799</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>48112</t>
+          <t>47365</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>79073</t>
+          <t>78033</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>147546</t>
+          <t>147237</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>195680</t>
+          <t>199444</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>40669</t>
+          <t>41478</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>71872</t>
+          <t>70364</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16623</t>
+          <t>17059</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>36892</t>
+          <t>38337</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>63783</t>
+          <t>63803</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>100443</t>
+          <t>98546</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>560469</t>
+          <t>558250</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>586655</t>
+          <t>586169</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>654110</t>
+          <t>655129</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>684064</t>
+          <t>684323</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1224730</t>
+          <t>1223733</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1263943</t>
+          <t>1264623</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,06%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>23311</t>
+          <t>23274</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>47947</t>
+          <t>49372</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9542,7 +9542,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>31504</t>
+          <t>30698</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>57271</t>
+          <t>55681</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>60383</t>
+          <t>60354</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>94887</t>
+          <t>97198</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3400</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16106</t>
+          <t>16067</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,7 +9650,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8189</t>
+          <t>8145</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22548</t>
+          <t>23858</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14626</t>
+          <t>13921</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33797</t>
+          <t>33473</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -9865,12 +9865,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>257351</t>
+          <t>258148</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>274362</t>
+          <t>274919</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>910643</t>
+          <t>912188</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>956587</t>
+          <t>958796</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1179771</t>
+          <t>1176948</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1229409</t>
+          <t>1224642</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>89,96%</t>
         </is>
       </c>
     </row>
@@ -9978,12 +9978,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8600</t>
+          <t>8364</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>25784</t>
+          <t>24312</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9993,12 +9993,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>79347</t>
+          <t>76259</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>117920</t>
+          <t>115835</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>91067</t>
+          <t>93913</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>134459</t>
+          <t>134236</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -10096,7 +10096,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7470</t>
+          <t>6554</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>32676</t>
+          <t>30875</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>60016</t>
+          <t>58479</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>34408</t>
+          <t>33461</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>62685</t>
+          <t>62520</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2954501</t>
+          <t>2951733</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3028174</t>
+          <t>3027282</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3082722</t>
+          <t>3085785</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3155912</t>
+          <t>3156402</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6061057</t>
+          <t>6062604</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6160825</t>
+          <t>6165485</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,93%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>243105</t>
+          <t>241193</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>308362</t>
+          <t>306273</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>239145</t>
+          <t>240111</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>305160</t>
+          <t>304422</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>500174</t>
+          <t>495839</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>587203</t>
+          <t>586794</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>75363</t>
+          <t>77248</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>114332</t>
+          <t>114788</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>87105</t>
+          <t>88905</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>126769</t>
+          <t>127741</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>172230</t>
+          <t>169580</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>228444</t>
+          <t>227806</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -10816,7 +10816,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su barrio se encuentra afectado por alguna industria contaminante en 2023</t>
+          <t>Población según si su barrio se encuentra afectado por alguna industria contaminante en 2023 (tasa de respuesta: 99,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11011,12 +11011,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>467916</t>
+          <t>467025</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>487763</t>
+          <t>487585</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11026,82 +11026,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>96,69%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>426344</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>413739</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>432520</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>96,09%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>93,25%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>97,48%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1182</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>905806</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>890370</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>916889</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>95,55%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>93,92%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>96,72%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>655</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>426344</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>414402</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>433634</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>96,09%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>93,4%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>97,73%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1182</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>905806</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>891711</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>916712</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>95,55%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>94,06%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>96,7%</t>
         </is>
       </c>
     </row>
@@ -11124,12 +11124,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10008</t>
+          <t>9552</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24888</t>
+          <t>24180</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11139,12 +11139,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11159,12 +11159,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7781</t>
+          <t>8281</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26994</t>
+          <t>25220</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11174,12 +11174,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11194,12 +11194,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20767</t>
+          <t>20162</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42923</t>
+          <t>43609</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11209,12 +11209,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>3746</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17995</t>
+          <t>18563</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8351</t>
+          <t>7180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11292,7 +11292,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6936</t>
+          <t>6502</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22909</t>
+          <t>21692</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -11467,12 +11467,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>424545</t>
+          <t>425512</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>441241</t>
+          <t>442016</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11482,12 +11482,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11502,12 +11502,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>356135</t>
+          <t>355539</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>369641</t>
+          <t>369624</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11517,12 +11517,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11537,12 +11537,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>786594</t>
+          <t>785927</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>807490</t>
+          <t>807161</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11552,12 +11552,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,85%</t>
         </is>
       </c>
     </row>
@@ -11580,12 +11580,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7783</t>
+          <t>7481</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22253</t>
+          <t>22756</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7859</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19234</t>
+          <t>20016</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11630,12 +11630,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11650,12 +11650,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>17506</t>
+          <t>18005</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>36687</t>
+          <t>36280</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9360</t>
+          <t>9753</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2263</t>
+          <t>2527</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10124</t>
+          <t>9820</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>4672</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16387</t>
+          <t>15306</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -11923,12 +11923,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>617584</t>
+          <t>619875</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>657907</t>
+          <t>658936</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11958,12 +11958,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>144793</t>
+          <t>144122</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>158454</t>
+          <t>158073</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11973,12 +11973,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11993,12 +11993,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>771547</t>
+          <t>772582</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>819161</t>
+          <t>818503</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -12036,12 +12036,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6414</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40676</t>
+          <t>40739</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12051,12 +12051,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4779</t>
+          <t>4887</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18101</t>
+          <t>18475</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10549</t>
+          <t>12318</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49324</t>
+          <t>49576</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>639</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12020</t>
+          <t>11986</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6921</t>
+          <t>7021</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2641</t>
+          <t>2717</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16452</t>
+          <t>16016</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -12379,12 +12379,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>971281</t>
+          <t>970582</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>998094</t>
+          <t>998666</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12394,12 +12394,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>922697</t>
+          <t>920746</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>958719</t>
+          <t>958395</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12429,12 +12429,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1902289</t>
+          <t>1903439</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1948857</t>
+          <t>1951740</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12464,12 +12464,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,15%</t>
         </is>
       </c>
     </row>
@@ -12492,12 +12492,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23591</t>
+          <t>22171</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>47190</t>
+          <t>48859</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12527,12 +12527,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14091</t>
+          <t>13122</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40951</t>
+          <t>41464</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12542,12 +12542,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>42342</t>
+          <t>41103</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>79106</t>
+          <t>78635</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7038</t>
+          <t>6705</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20599</t>
+          <t>20757</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12620,49 +12620,49 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>10799</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>4838</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>19543</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
           <t>2,0%</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>10799</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>4923</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>18462</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>29</t>
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13739</t>
+          <t>14450</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>35218</t>
+          <t>35833</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -12835,12 +12835,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>439358</t>
+          <t>438923</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>458311</t>
+          <t>458576</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12850,12 +12850,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12870,12 +12870,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>792678</t>
+          <t>792965</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>812923</t>
+          <t>813333</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12885,12 +12885,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1238745</t>
+          <t>1237470</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1267546</t>
+          <t>1267667</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,79%</t>
         </is>
       </c>
     </row>
@@ -12948,12 +12948,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8103</t>
+          <t>8543</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>22938</t>
+          <t>23285</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12963,12 +12963,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17844</t>
+          <t>17696</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>36183</t>
+          <t>34960</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13018,12 +13018,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>30177</t>
+          <t>29664</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>53353</t>
+          <t>53635</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13033,12 +13033,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4558</t>
+          <t>4132</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16520</t>
+          <t>16741</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2825</t>
+          <t>2762</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11015</t>
+          <t>11118</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8731</t>
+          <t>9295</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23343</t>
+          <t>24382</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -13291,12 +13291,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>201845</t>
+          <t>201489</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>232322</t>
+          <t>232014</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13306,12 +13306,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13326,12 +13326,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>714404</t>
+          <t>714316</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>735931</t>
+          <t>736095</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13341,12 +13341,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>923596</t>
+          <t>927816</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>961725</t>
+          <t>962627</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13376,12 +13376,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,19%</t>
         </is>
       </c>
     </row>
@@ -13404,12 +13404,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4746</t>
+          <t>4658</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>29640</t>
+          <t>30875</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13419,12 +13419,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13439,12 +13439,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>18492</t>
+          <t>18504</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>35930</t>
+          <t>36045</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13459,7 +13459,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13474,12 +13474,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>27218</t>
+          <t>27898</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>57293</t>
+          <t>57032</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -13522,7 +13522,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20751</t>
+          <t>23181</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13552,12 +13552,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2874</t>
+          <t>3453</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>17747</t>
+          <t>19089</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13567,12 +13567,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13587,12 +13587,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6020</t>
+          <t>5903</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>30072</t>
+          <t>31002</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13602,12 +13602,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -13747,12 +13747,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3182189</t>
+          <t>3179743</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3248749</t>
+          <t>3248411</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13762,12 +13762,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13782,12 +13782,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3386451</t>
+          <t>3384411</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3440577</t>
+          <t>3438317</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13797,12 +13797,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13817,12 +13817,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6579805</t>
+          <t>6580748</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6670622</t>
+          <t>6669036</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13832,12 +13832,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,18%</t>
         </is>
       </c>
     </row>
@@ -13860,12 +13860,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>84917</t>
+          <t>84987</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>137502</t>
+          <t>138467</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>92907</t>
+          <t>93942</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>138126</t>
+          <t>139174</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13910,12 +13910,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>192999</t>
+          <t>196053</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>263401</t>
+          <t>267974</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13945,12 +13945,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -13973,12 +13973,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>30719</t>
+          <t>31632</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>65759</t>
+          <t>65317</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13988,12 +13988,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>26254</t>
+          <t>26118</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>49315</t>
+          <t>49701</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14023,12 +14023,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>64817</t>
+          <t>62197</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>104933</t>
+          <t>102839</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P05A04-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P05A04-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>404572</t>
+          <t>404522</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>431049</t>
+          <t>430849</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>255953</t>
+          <t>254871</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>278694</t>
+          <t>278526</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>668565</t>
+          <t>666299</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>703147</t>
+          <t>703369</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,94%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24489</t>
+          <t>25096</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47571</t>
+          <t>47677</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21186</t>
+          <t>21541</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42543</t>
+          <t>43945</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51898</t>
+          <t>52318</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>82164</t>
+          <t>83843</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,84%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7601</t>
+          <t>7971</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23367</t>
+          <t>24171</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2287</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13517</t>
+          <t>13180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12412</t>
+          <t>12727</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30058</t>
+          <t>31282</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>305335</t>
+          <t>305469</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>332104</t>
+          <t>331727</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>323741</t>
+          <t>323532</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>346127</t>
+          <t>346533</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>636364</t>
+          <t>636882</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>672499</t>
+          <t>673268</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,75%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25799</t>
+          <t>26167</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51406</t>
+          <t>51057</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15342</t>
+          <t>16208</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34710</t>
+          <t>36550</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>46542</t>
+          <t>46414</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>77873</t>
+          <t>77427</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,55%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>3285</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15858</t>
+          <t>15127</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4040</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16504</t>
+          <t>16806</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9505</t>
+          <t>9847</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27265</t>
+          <t>27258</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>458159</t>
+          <t>459733</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>488580</t>
+          <t>489606</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>144154</t>
+          <t>145030</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>159929</t>
+          <t>160194</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>612461</t>
+          <t>610132</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>645242</t>
+          <t>643696</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,35%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40120</t>
+          <t>40050</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67840</t>
+          <t>66011</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7142</t>
+          <t>7048</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22116</t>
+          <t>21630</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>49866</t>
+          <t>52139</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>81223</t>
+          <t>83790</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3901</t>
+          <t>4339</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18636</t>
+          <t>19129</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4662</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>20830</t>
+          <t>21564</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1074193</t>
+          <t>1075648</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1117758</t>
+          <t>1118775</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>621867</t>
+          <t>620277</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>652828</t>
+          <t>652131</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1707144</t>
+          <t>1706731</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1760332</t>
+          <t>1762409</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,18%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>93078</t>
+          <t>92165</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>134151</t>
+          <t>133829</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39982</t>
+          <t>39475</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>68752</t>
+          <t>68448</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>141844</t>
+          <t>139691</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>191523</t>
+          <t>190605</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10257</t>
+          <t>10543</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27091</t>
+          <t>26410</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9696</t>
+          <t>9623</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>24521</t>
+          <t>25689</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>22956</t>
+          <t>23338</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>44497</t>
+          <t>45699</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>295543</t>
+          <t>294286</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>318362</t>
+          <t>317698</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>471737</t>
+          <t>471474</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>505400</t>
+          <t>505312</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>776030</t>
+          <t>775745</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>815497</t>
+          <t>815956</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,63%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20353</t>
+          <t>20777</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>40295</t>
+          <t>40526</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>47392</t>
+          <t>47824</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>78841</t>
+          <t>78416</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>73804</t>
+          <t>74097</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>110290</t>
+          <t>110984</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,19%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16617</t>
+          <t>15880</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7048</t>
+          <t>7098</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21717</t>
+          <t>22137</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13947</t>
+          <t>14100</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>32419</t>
+          <t>33247</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -2993,7 +2993,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>262779</t>
+          <t>262303</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>280923</t>
+          <t>280882</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1076099</t>
+          <t>1074404</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1119363</t>
+          <t>1119126</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1347274</t>
+          <t>1346179</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1394670</t>
+          <t>1396006</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,37%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13931</t>
+          <t>13852</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>31354</t>
+          <t>32926</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>88038</t>
+          <t>86283</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>126504</t>
+          <t>126678</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>104639</t>
+          <t>104555</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>150353</t>
+          <t>149875</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6463</t>
+          <t>6156</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>17778</t>
+          <t>18005</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>38052</t>
+          <t>39659</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>19493</t>
+          <t>19084</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>41785</t>
+          <t>41909</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2852518</t>
+          <t>2856059</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2923594</t>
+          <t>2927608</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2944731</t>
+          <t>2950433</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3019252</t>
+          <t>3021356</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5829747</t>
+          <t>5821535</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5928184</t>
+          <t>5926800</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,03%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>257207</t>
+          <t>256468</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>325849</t>
+          <t>323046</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>255676</t>
+          <t>253075</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>321514</t>
+          <t>319853</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>529950</t>
+          <t>528680</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>622028</t>
+          <t>621664</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>43877</t>
+          <t>44652</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>75135</t>
+          <t>77455</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>57070</t>
+          <t>57922</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>91252</t>
+          <t>90888</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>109644</t>
+          <t>108265</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>154669</t>
+          <t>155271</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>387512</t>
+          <t>387557</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>410324</t>
+          <t>411107</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>268984</t>
+          <t>269593</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>289753</t>
+          <t>290620</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>663704</t>
+          <t>663813</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>695132</t>
+          <t>695691</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,51%</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14658</t>
+          <t>15384</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34000</t>
+          <t>35039</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11582</t>
+          <t>11260</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29415</t>
+          <t>30322</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30636</t>
+          <t>30944</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57223</t>
+          <t>58660</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7314</t>
+          <t>6061</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21452</t>
+          <t>21023</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3629</t>
+          <t>3610</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14995</t>
+          <t>14092</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12339</t>
+          <t>11964</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30524</t>
+          <t>30312</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>345627</t>
+          <t>345114</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>376270</t>
+          <t>376039</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>289096</t>
+          <t>290539</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>312019</t>
+          <t>313248</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>643622</t>
+          <t>644399</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>681521</t>
+          <t>682660</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,25%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24458</t>
+          <t>25198</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>49758</t>
+          <t>52262</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18814</t>
+          <t>17689</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39423</t>
+          <t>38483</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>48741</t>
+          <t>47598</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>83095</t>
+          <t>80904</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7941</t>
+          <t>7168</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27232</t>
+          <t>25763</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>1913</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13568</t>
+          <t>14269</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11245</t>
+          <t>11233</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32573</t>
+          <t>31609</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>558570</t>
+          <t>558128</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>587672</t>
+          <t>588764</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>232100</t>
+          <t>229644</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>246969</t>
+          <t>246796</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>798240</t>
+          <t>796666</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>831402</t>
+          <t>829596</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,21%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31374</t>
+          <t>30247</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60172</t>
+          <t>59078</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6006</t>
+          <t>5913</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18500</t>
+          <t>20284</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40501</t>
+          <t>41776</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>71372</t>
+          <t>71277</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2979</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14514</t>
+          <t>14465</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10102</t>
+          <t>11549</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>4983</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19350</t>
+          <t>19004</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1038194</t>
+          <t>1036343</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1077497</t>
+          <t>1075713</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>673476</t>
+          <t>672603</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>706733</t>
+          <t>706503</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1720897</t>
+          <t>1720978</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1772283</t>
+          <t>1774530</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,83%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>51267</t>
+          <t>51449</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>85861</t>
+          <t>86425</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41439</t>
+          <t>41243</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>70035</t>
+          <t>71258</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>100239</t>
+          <t>101042</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>144619</t>
+          <t>147430</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15983</t>
+          <t>16884</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>37642</t>
+          <t>38194</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>7939</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25339</t>
+          <t>24154</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>28364</t>
+          <t>28187</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>54384</t>
+          <t>55012</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>452847</t>
+          <t>452537</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>476812</t>
+          <t>476796</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>680130</t>
+          <t>679971</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>711539</t>
+          <t>710411</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1143157</t>
+          <t>1144862</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1182243</t>
+          <t>1182497</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,81%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20945</t>
+          <t>21550</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>42394</t>
+          <t>43320</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>34859</t>
+          <t>35098</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>62519</t>
+          <t>62284</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>61251</t>
+          <t>61624</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>97541</t>
+          <t>96196</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3841</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16681</t>
+          <t>15799</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4855</t>
+          <t>5694</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18288</t>
+          <t>20536</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10647</t>
+          <t>11780</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>28539</t>
+          <t>30694</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6419,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>227253</t>
+          <t>226811</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>246694</t>
+          <t>245800</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>978341</t>
+          <t>977977</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1016641</t>
+          <t>1017737</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,47 +6489,47 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
+          <t>92,41%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>1175</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>1236591</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>1216501</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>1260064</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>90,59%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>89,12%</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
           <t>92,31%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>1175</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>1236591</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>1212627</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>1257554</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>90,59%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>88,84%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>92,13%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15536</t>
+          <t>15852</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>33958</t>
+          <t>34457</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>66350</t>
+          <t>65920</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>102038</t>
+          <t>100380</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>87350</t>
+          <t>86512</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>127757</t>
+          <t>125441</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6741</t>
+          <t>6627</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12100</t>
+          <t>12248</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>30140</t>
+          <t>29461</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>13848</t>
+          <t>14451</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>33868</t>
+          <t>33158</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3061529</t>
+          <t>3067580</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3131212</t>
+          <t>3135879</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3177001</t>
+          <t>3177000</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3246936</t>
+          <t>3244231</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6266091</t>
+          <t>6266325</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6357607</t>
+          <t>6359694</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,04%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>197366</t>
+          <t>193310</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>258641</t>
+          <t>255274</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>212709</t>
+          <t>211486</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>274651</t>
+          <t>274203</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>424848</t>
+          <t>424727</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>510072</t>
+          <t>506973</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7098,7 +7098,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>53567</t>
+          <t>54395</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>89304</t>
+          <t>89336</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,77 +7136,77 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>60887</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>47207</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>79910</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>130710</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>109464</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>156509</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
           <t>1,58%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>2,63%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>60887</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>46214</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>78973</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>130710</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>108701</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>156858</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -7585,12 +7585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>372444</t>
+          <t>372375</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>396884</t>
+          <t>397072</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>293861</t>
+          <t>293830</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>317527</t>
+          <t>317202</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>673700</t>
+          <t>674500</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>710493</t>
+          <t>708710</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,12%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21933</t>
+          <t>22722</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45421</t>
+          <t>46576</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16399</t>
+          <t>17008</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36611</t>
+          <t>35950</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43424</t>
+          <t>44439</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>76053</t>
+          <t>75194</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3041</t>
+          <t>3024</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14136</t>
+          <t>13912</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5891</t>
+          <t>5589</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18782</t>
+          <t>19616</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11609</t>
+          <t>11435</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>28880</t>
+          <t>28841</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>320919</t>
+          <t>321628</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>345295</t>
+          <t>346914</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>311097</t>
+          <t>311838</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>337590</t>
+          <t>336490</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>640428</t>
+          <t>641606</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>678817</t>
+          <t>676866</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,31%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22075</t>
+          <t>21721</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>44321</t>
+          <t>44809</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22453</t>
+          <t>23138</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>45696</t>
+          <t>45664</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>47423</t>
+          <t>50033</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>81315</t>
+          <t>81572</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,0%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3108</t>
+          <t>3087</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13834</t>
+          <t>14518</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8287,7 +8287,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3375</t>
+          <t>3927</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15625</t>
+          <t>16724</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8909</t>
+          <t>9112</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24769</t>
+          <t>25181</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>436085</t>
+          <t>433293</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>465010</t>
+          <t>466300</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>140530</t>
+          <t>142124</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>157427</t>
+          <t>157531</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>583891</t>
+          <t>582870</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>617272</t>
+          <t>618439</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,65%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37734</t>
+          <t>36434</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63516</t>
+          <t>66435</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6206</t>
+          <t>6507</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21953</t>
+          <t>20584</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>48113</t>
+          <t>47638</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>78314</t>
+          <t>79846</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8434</t>
+          <t>8297</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23654</t>
+          <t>23236</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>963</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8124</t>
+          <t>9164</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10725</t>
+          <t>10028</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>27668</t>
+          <t>27074</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>950927</t>
+          <t>952388</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>999285</t>
+          <t>999332</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>713309</t>
+          <t>709274</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>746989</t>
+          <t>745761</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1673255</t>
+          <t>1674790</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1735124</t>
+          <t>1735260</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,68%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>90191</t>
+          <t>90093</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>132799</t>
+          <t>127920</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>47365</t>
+          <t>48840</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>78033</t>
+          <t>79072</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>147237</t>
+          <t>146203</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>199444</t>
+          <t>196986</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>41478</t>
+          <t>41418</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>70364</t>
+          <t>73127</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17059</t>
+          <t>16992</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>38337</t>
+          <t>36066</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>63803</t>
+          <t>63916</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>98546</t>
+          <t>99803</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>558250</t>
+          <t>560856</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>586169</t>
+          <t>587250</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>655129</t>
+          <t>655606</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>684323</t>
+          <t>686030</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1223733</t>
+          <t>1225324</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1264623</t>
+          <t>1264687</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,07%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>23274</t>
+          <t>22338</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>49372</t>
+          <t>46856</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>30698</t>
+          <t>29459</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>55681</t>
+          <t>55903</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>60354</t>
+          <t>59299</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>97198</t>
+          <t>95361</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>3715</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16067</t>
+          <t>15962</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8145</t>
+          <t>7989</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23858</t>
+          <t>23403</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13921</t>
+          <t>13903</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33473</t>
+          <t>33120</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -9845,7 +9845,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>258148</t>
+          <t>257713</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>274919</t>
+          <t>274629</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>912188</t>
+          <t>914204</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>958796</t>
+          <t>956613</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1176948</t>
+          <t>1176752</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1224642</t>
+          <t>1225901</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,05%</t>
         </is>
       </c>
     </row>
@@ -9978,12 +9978,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8364</t>
+          <t>8984</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24312</t>
+          <t>25446</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9993,12 +9993,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>76259</t>
+          <t>79291</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>115835</t>
+          <t>116947</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>93913</t>
+          <t>92765</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>134236</t>
+          <t>134532</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -10096,7 +10096,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6554</t>
+          <t>6846</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>30875</t>
+          <t>32112</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>58479</t>
+          <t>59799</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>33461</t>
+          <t>33362</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>62520</t>
+          <t>60498</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2951733</t>
+          <t>2958131</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3027282</t>
+          <t>3028108</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3085785</t>
+          <t>3084345</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3156402</t>
+          <t>3159390</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6062604</t>
+          <t>6053103</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6165485</t>
+          <t>6162940</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,9%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>241193</t>
+          <t>238762</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>306273</t>
+          <t>302364</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>240111</t>
+          <t>240279</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>304422</t>
+          <t>305284</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>495839</t>
+          <t>499052</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>586794</t>
+          <t>587932</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>77248</t>
+          <t>75276</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>114788</t>
+          <t>115337</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>88905</t>
+          <t>85990</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>127741</t>
+          <t>126156</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>169580</t>
+          <t>174621</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>227806</t>
+          <t>230980</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -11006,32 +11006,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>479462</t>
+          <t>523298</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>467025</t>
+          <t>510884</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>487585</t>
+          <t>531991</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11041,32 +11041,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>426344</t>
+          <t>462765</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>413739</t>
+          <t>447889</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>432520</t>
+          <t>469010</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11076,32 +11076,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>905806</t>
+          <t>986062</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>890370</t>
+          <t>968729</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>916889</t>
+          <t>997894</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,71%</t>
         </is>
       </c>
     </row>
@@ -11119,32 +11119,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15909</t>
+          <t>16919</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9552</t>
+          <t>10236</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24180</t>
+          <t>26459</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11154,32 +11154,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13959</t>
+          <t>15313</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8281</t>
+          <t>9348</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25220</t>
+          <t>29294</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11189,32 +11189,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>29869</t>
+          <t>32232</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20162</t>
+          <t>23123</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43609</t>
+          <t>48421</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -11232,32 +11232,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8931</t>
+          <t>9440</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3746</t>
+          <t>4386</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18563</t>
+          <t>19879</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11267,32 +11267,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3403</t>
+          <t>4115</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>1527</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7180</t>
+          <t>8172</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11302,32 +11302,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>12334</t>
+          <t>13555</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6502</t>
+          <t>7893</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21692</t>
+          <t>25281</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -11345,17 +11345,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>504302</t>
+          <t>549657</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>504302</t>
+          <t>549657</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>504302</t>
+          <t>549657</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11380,17 +11380,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>443707</t>
+          <t>482193</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>443707</t>
+          <t>482193</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>443707</t>
+          <t>482193</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11415,17 +11415,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>948009</t>
+          <t>1031850</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>948009</t>
+          <t>1031850</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>948009</t>
+          <t>1031850</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11462,32 +11462,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>435087</t>
+          <t>465261</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>425512</t>
+          <t>456133</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>442016</t>
+          <t>472578</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11497,32 +11497,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>363236</t>
+          <t>402588</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>355539</t>
+          <t>394177</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>369624</t>
+          <t>408946</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11532,32 +11532,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>798322</t>
+          <t>867849</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>785927</t>
+          <t>856644</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>807161</t>
+          <t>878407</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>97,07%</t>
         </is>
       </c>
     </row>
@@ -11575,32 +11575,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13104</t>
+          <t>13824</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7481</t>
+          <t>7704</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22756</t>
+          <t>21762</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11610,32 +11610,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12729</t>
+          <t>13880</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>8705</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20016</t>
+          <t>21640</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11645,32 +11645,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>25833</t>
+          <t>27704</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>18005</t>
+          <t>18753</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>36280</t>
+          <t>37906</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -11688,32 +11688,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>4127</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9753</t>
+          <t>10037</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2527</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9820</t>
+          <t>10204</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>9258</t>
+          <t>9361</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4672</t>
+          <t>5136</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15306</t>
+          <t>16406</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -11801,17 +11801,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11836,17 +11836,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>381201</t>
+          <t>421702</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>381201</t>
+          <t>421702</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>381201</t>
+          <t>421702</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11871,17 +11871,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>833413</t>
+          <t>904914</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>833413</t>
+          <t>904914</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>833413</t>
+          <t>904914</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11918,32 +11918,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>639783</t>
+          <t>436581</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>619875</t>
+          <t>422824</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>658936</t>
+          <t>447152</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11953,32 +11953,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>153653</t>
+          <t>172865</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>144122</t>
+          <t>162403</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>158073</t>
+          <t>177873</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11988,32 +11988,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>793436</t>
+          <t>609446</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>772582</t>
+          <t>592482</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>818503</t>
+          <t>621697</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>94,65%</t>
         </is>
       </c>
     </row>
@@ -12031,32 +12031,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22554</t>
+          <t>27798</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>18216</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40739</t>
+          <t>39957</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8942</t>
+          <t>9896</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4887</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18475</t>
+          <t>20138</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>31496</t>
+          <t>37693</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12318</t>
+          <t>26209</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49576</t>
+          <t>53346</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -12144,32 +12144,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4922</t>
+          <t>6298</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11986</t>
+          <t>13484</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12179,32 +12179,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>3412</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1242</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7021</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>8134</t>
+          <t>9710</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2717</t>
+          <t>5031</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16016</t>
+          <t>17827</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -12257,17 +12257,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>667259</t>
+          <t>470677</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>667259</t>
+          <t>470677</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>667259</t>
+          <t>470677</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12292,17 +12292,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>165807</t>
+          <t>186172</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>165807</t>
+          <t>186172</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>165807</t>
+          <t>186172</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>833066</t>
+          <t>656849</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>833066</t>
+          <t>656849</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>833066</t>
+          <t>656849</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12374,32 +12374,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>986086</t>
+          <t>1076787</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>970582</t>
+          <t>1058096</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>998666</t>
+          <t>1089849</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12409,32 +12409,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>937479</t>
+          <t>816485</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>920746</t>
+          <t>802646</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>958395</t>
+          <t>827031</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12444,32 +12444,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1923564</t>
+          <t>1893272</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1903439</t>
+          <t>1871660</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1951740</t>
+          <t>1908855</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -12487,32 +12487,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>33710</t>
+          <t>37650</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22171</t>
+          <t>26717</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>48859</t>
+          <t>53846</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12522,32 +12522,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>28474</t>
+          <t>30993</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13122</t>
+          <t>22099</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>41464</t>
+          <t>41577</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12557,32 +12557,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>62184</t>
+          <t>68643</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>41103</t>
+          <t>54941</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>78635</t>
+          <t>87426</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -12600,32 +12600,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12414</t>
+          <t>13815</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6705</t>
+          <t>7888</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20757</t>
+          <t>22933</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12635,32 +12635,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10799</t>
+          <t>12338</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4838</t>
+          <t>6836</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19543</t>
+          <t>20287</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12670,32 +12670,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>23213</t>
+          <t>26153</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>14450</t>
+          <t>17545</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>35833</t>
+          <t>38118</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -12713,17 +12713,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1032210</t>
+          <t>1128252</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1032210</t>
+          <t>1128252</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1032210</t>
+          <t>1128252</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12748,17 +12748,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>976752</t>
+          <t>859816</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>976752</t>
+          <t>859816</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>976752</t>
+          <t>859816</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12783,17 +12783,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2008961</t>
+          <t>1988068</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2008961</t>
+          <t>1988068</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2008961</t>
+          <t>1988068</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12830,32 +12830,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>451202</t>
+          <t>542320</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>438923</t>
+          <t>529960</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>458576</t>
+          <t>550979</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12865,32 +12865,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>803652</t>
+          <t>790070</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>792965</t>
+          <t>779350</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>813333</t>
+          <t>798288</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12900,32 +12900,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1254855</t>
+          <t>1332390</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1237470</t>
+          <t>1317296</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1267667</t>
+          <t>1344298</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,62%</t>
         </is>
       </c>
     </row>
@@ -12943,32 +12943,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14103</t>
+          <t>15394</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8543</t>
+          <t>8658</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>23285</t>
+          <t>24908</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12978,32 +12978,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>26071</t>
+          <t>28276</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17696</t>
+          <t>20632</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>34960</t>
+          <t>37754</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13013,32 +13013,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>40174</t>
+          <t>43670</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>29664</t>
+          <t>33385</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>53635</t>
+          <t>55853</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -13056,32 +13056,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>8743</t>
+          <t>9262</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4132</t>
+          <t>4241</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16741</t>
+          <t>18832</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13091,32 +13091,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>6072</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2762</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11118</t>
+          <t>11426</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13126,32 +13126,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>14719</t>
+          <t>15334</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>9376</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24382</t>
+          <t>23536</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -13169,17 +13169,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13204,17 +13204,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>835699</t>
+          <t>824418</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>835699</t>
+          <t>824418</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>835699</t>
+          <t>824418</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13239,17 +13239,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1309748</t>
+          <t>1391394</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1309748</t>
+          <t>1391394</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1309748</t>
+          <t>1391394</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -13286,32 +13286,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>221107</t>
+          <t>217341</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>201489</t>
+          <t>199783</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>232014</t>
+          <t>228338</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13321,32 +13321,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>726719</t>
+          <t>805232</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>714316</t>
+          <t>791448</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>736095</t>
+          <t>815845</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13356,32 +13356,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>947826</t>
+          <t>1022573</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>927816</t>
+          <t>1002926</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>962627</t>
+          <t>1038434</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,13%</t>
         </is>
       </c>
     </row>
@@ -13399,32 +13399,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>13214</t>
+          <t>14720</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4658</t>
+          <t>5370</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>30875</t>
+          <t>31171</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13434,32 +13434,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>25783</t>
+          <t>29925</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>18504</t>
+          <t>21119</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>36045</t>
+          <t>41885</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13469,32 +13469,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>38997</t>
+          <t>44645</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>27898</t>
+          <t>31105</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>57032</t>
+          <t>62335</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -13512,7 +13512,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>6186</t>
+          <t>5167</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -13522,12 +13522,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>23181</t>
+          <t>17830</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13547,32 +13547,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t>7907</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3453</t>
+          <t>3142</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>19089</t>
+          <t>17455</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13582,32 +13582,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>13918</t>
+          <t>13074</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5903</t>
+          <t>6036</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>31002</t>
+          <t>27278</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -13625,17 +13625,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13660,17 +13660,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>760234</t>
+          <t>843064</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>760234</t>
+          <t>843064</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>760234</t>
+          <t>843064</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13695,17 +13695,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1000741</t>
+          <t>1080292</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1000741</t>
+          <t>1080292</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1000741</t>
+          <t>1080292</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13742,32 +13742,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3212727</t>
+          <t>3261587</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3179743</t>
+          <t>3232062</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3248411</t>
+          <t>3288934</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13777,32 +13777,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3411083</t>
+          <t>3450004</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3384411</t>
+          <t>3426677</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3438317</t>
+          <t>3470951</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13812,32 +13812,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>6623810</t>
+          <t>6711591</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6580748</t>
+          <t>6673033</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6669036</t>
+          <t>6745601</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>95,64%</t>
         </is>
       </c>
     </row>
@@ -13855,32 +13855,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>112594</t>
+          <t>126305</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>84987</t>
+          <t>103424</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>138467</t>
+          <t>152298</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13890,32 +13890,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>115959</t>
+          <t>128283</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>93942</t>
+          <t>110656</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>139174</t>
+          <t>153134</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13925,32 +13925,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>228553</t>
+          <t>254588</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>196053</t>
+          <t>222476</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>267974</t>
+          <t>288431</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -13968,32 +13968,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>45218</t>
+          <t>48109</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>31632</t>
+          <t>34805</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>65317</t>
+          <t>66921</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14003,32 +14003,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>36358</t>
+          <t>39079</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>26118</t>
+          <t>29259</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>49701</t>
+          <t>51491</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14038,32 +14038,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>81576</t>
+          <t>87188</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>62197</t>
+          <t>69505</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>102839</t>
+          <t>109701</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -14081,17 +14081,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3370540</t>
+          <t>3436002</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3370540</t>
+          <t>3436002</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3370540</t>
+          <t>3436002</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14116,17 +14116,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3563399</t>
+          <t>3617365</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3563399</t>
+          <t>3617365</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3563399</t>
+          <t>3617365</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14151,17 +14151,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>6933939</t>
+          <t>7053367</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6933939</t>
+          <t>7053367</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6933939</t>
+          <t>7053367</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
